--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-20).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-20).xlsx
@@ -915,66 +915,66 @@
   </si>
   <si>
     <t>215
-145</t>
-  </si>
-  <si>
-    <t>61</t>
-  </si>
-  <si>
-    <t>R$ 790.316,69</t>
-  </si>
-  <si>
-    <t>R$ 5.131,93
-R$ 5.195,62</t>
-  </si>
-  <si>
-    <t>(3.4%)
-(2.2%)</t>
-  </si>
-  <si>
-    <t>54.5</t>
-  </si>
-  <si>
-    <t>(5.0%)</t>
-  </si>
-  <si>
-    <t>34.2%</t>
-  </si>
-  <si>
-    <t>(3.8%)</t>
-  </si>
-  <si>
-    <t>3.2%</t>
-  </si>
-  <si>
-    <t>0.3%</t>
-  </si>
-  <si>
-    <t>26.0</t>
-  </si>
-  <si>
-    <t>75.4%</t>
-  </si>
-  <si>
-    <t>6.8%</t>
-  </si>
-  <si>
-    <t>5.1</t>
-  </si>
-  <si>
-    <t>6.1</t>
-  </si>
-  <si>
-    <t>11.2</t>
-  </si>
-  <si>
-    <t>18.0</t>
-  </si>
-  <si>
-    <t>75.6%</t>
-  </si>
-  <si>
-    <t>-R$ 25.109,19</t>
+178</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>R$ 955.177,29</t>
+  </si>
+  <si>
+    <t>R$ 5.027,25
+R$ 5.119,53</t>
+  </si>
+  <si>
+    <t>(3.2%)
+(1.4%)</t>
+  </si>
+  <si>
+    <t>53.4</t>
+  </si>
+  <si>
+    <t>(5.2%)</t>
+  </si>
+  <si>
+    <t>35.4%</t>
+  </si>
+  <si>
+    <t>(3.3%)</t>
+  </si>
+  <si>
+    <t>3.5%</t>
+  </si>
+  <si>
+    <t>0.5%</t>
+  </si>
+  <si>
+    <t>26.2</t>
+  </si>
+  <si>
+    <t>74.4%</t>
+  </si>
+  <si>
+    <t>7.4%</t>
+  </si>
+  <si>
+    <t>5.3</t>
+  </si>
+  <si>
+    <t>6.2</t>
+  </si>
+  <si>
+    <t>11.5</t>
+  </si>
+  <si>
+    <t>18.2</t>
+  </si>
+  <si>
+    <t>74.9%</t>
+  </si>
+  <si>
+    <t>-R$ 30.103,32</t>
   </si>
   <si>
     <t>2.94</t>
@@ -2069,7 +2069,7 @@
         <v>19507</v>
       </c>
       <c r="B6" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C6" s="4">
         <v>44</v>
@@ -2105,25 +2105,61 @@
       <c t="s" r="N6" s="4">
         <v>52</v>
       </c>
-      <c r="O6" s="5"/>
-      <c r="P6" s="5"/>
-      <c r="Q6" s="6"/>
-      <c r="R6" s="7"/>
-      <c r="S6" s="6"/>
-      <c r="T6" s="6"/>
-      <c r="U6" s="6"/>
-      <c r="V6" s="6"/>
-      <c r="W6" s="6"/>
-      <c r="X6" s="8"/>
-      <c r="Y6" s="6"/>
-      <c r="Z6" s="6"/>
-      <c r="AA6" s="8"/>
-      <c r="AB6" s="8"/>
-      <c r="AC6" s="8"/>
-      <c r="AD6" s="8"/>
-      <c r="AE6" s="6"/>
+      <c r="O6" s="5">
+        <v>11061.950000000001</v>
+      </c>
+      <c r="P6" s="5">
+        <v>11061.950000000001</v>
+      </c>
+      <c r="Q6" s="6">
+        <v>0.044681045970140332</v>
+      </c>
+      <c r="R6" s="7">
+        <v>104</v>
+      </c>
+      <c r="S6" s="6">
+        <v>-0.028037383177570097</v>
+      </c>
+      <c r="T6" s="6">
+        <v>0.36097658188655701</v>
+      </c>
+      <c r="U6" s="6">
+        <v>0.027234339334384985</v>
+      </c>
+      <c r="V6" s="6">
+        <v>0.034592734554034318</v>
+      </c>
+      <c r="W6" s="6">
+        <v>0.010244405371566494</v>
+      </c>
+      <c r="X6" s="8">
+        <v>19.993960869565218</v>
+      </c>
+      <c r="Y6" s="6">
+        <v>0.94285714285714284</v>
+      </c>
+      <c r="Z6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="8">
+        <v>5.1498362745098047</v>
+      </c>
+      <c r="AB6" s="8">
+        <v>1.5151955882352941</v>
+      </c>
+      <c r="AC6" s="8">
+        <v>6.6997369999999998</v>
+      </c>
+      <c r="AD6" s="8">
+        <v>13.592028985507246</v>
+      </c>
+      <c r="AE6" s="6">
+        <v>1</v>
+      </c>
       <c r="AF6" s="9"/>
-      <c r="AG6" s="5"/>
+      <c r="AG6" s="5">
+        <v>0</v>
+      </c>
       <c r="AH6" s="10">
         <v>5</v>
       </c>
@@ -2349,10 +2385,10 @@
         <v>0.053333333333333233</v>
       </c>
       <c r="T8" s="6">
-        <v>0.34587775125961284</v>
+        <v>0.34608342386577817</v>
       </c>
       <c r="U8" s="6">
-        <v>-0.020522022908272812</v>
+        <v>-0.020316350302107482</v>
       </c>
       <c r="V8" s="6">
         <v>0.035448156987536464</v>
@@ -2609,10 +2645,10 @@
         <v>0.47999999999999998</v>
       </c>
       <c r="T10" s="6">
-        <v>0.40516843471052533</v>
+        <v>0.39621808810985498</v>
       </c>
       <c r="U10" s="6">
-        <v>0.017805843555149751</v>
+        <v>0.0088554969544793766</v>
       </c>
       <c r="V10" s="6">
         <v>0.02596447493302257</v>
@@ -2688,7 +2724,7 @@
         <v>19513</v>
       </c>
       <c r="B11" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C11" s="4">
         <v>44</v>
@@ -2724,25 +2760,61 @@
       <c t="s" r="N11" s="4">
         <v>52</v>
       </c>
-      <c r="O11" s="5"/>
-      <c r="P11" s="5"/>
-      <c r="Q11" s="6"/>
-      <c r="R11" s="7"/>
-      <c r="S11" s="6"/>
-      <c r="T11" s="6"/>
-      <c r="U11" s="6"/>
-      <c r="V11" s="6"/>
-      <c r="W11" s="6"/>
-      <c r="X11" s="8"/>
-      <c r="Y11" s="6"/>
-      <c r="Z11" s="6"/>
-      <c r="AA11" s="8"/>
-      <c r="AB11" s="8"/>
-      <c r="AC11" s="8"/>
-      <c r="AD11" s="8"/>
-      <c r="AE11" s="6"/>
+      <c r="O11" s="5">
+        <v>10156.459999999999</v>
+      </c>
+      <c r="P11" s="5">
+        <v>10156.459999999999</v>
+      </c>
+      <c r="Q11" s="6">
+        <v>0.17893429445324682</v>
+      </c>
+      <c r="R11" s="7">
+        <v>90</v>
+      </c>
+      <c r="S11" s="6">
+        <v>0.034482758620689724</v>
+      </c>
+      <c r="T11" s="6">
+        <v>0.3302577079021628</v>
+      </c>
+      <c r="U11" s="6">
+        <v>0.018581198567217318</v>
+      </c>
+      <c r="V11" s="6">
+        <v>0.040504614796887897</v>
+      </c>
+      <c r="W11" s="6">
+        <v>0.01528224401021616</v>
+      </c>
+      <c r="X11" s="8">
+        <v>28.315079365079363</v>
+      </c>
+      <c r="Y11" s="6">
+        <v>0.44444444444444442</v>
+      </c>
+      <c r="Z11" s="6">
+        <v>0.079365079365079361</v>
+      </c>
+      <c r="AA11" s="8">
+        <v>6.1766304347826084</v>
+      </c>
+      <c r="AB11" s="8">
+        <v>6.8420634920634926</v>
+      </c>
+      <c r="AC11" s="8">
+        <v>13.104302000000001</v>
+      </c>
+      <c r="AD11" s="8">
+        <v>19.084392063492064</v>
+      </c>
+      <c r="AE11" s="6">
+        <v>0.63492063492063489</v>
+      </c>
       <c r="AF11" s="9"/>
-      <c r="AG11" s="5"/>
+      <c r="AG11" s="5">
+        <v>-282.80000000000001</v>
+      </c>
       <c r="AH11" s="10">
         <v>3</v>
       </c>
@@ -3176,7 +3248,7 @@
         <v>19519</v>
       </c>
       <c r="B15" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C15" s="4">
         <v>44</v>
@@ -3212,25 +3284,61 @@
       <c t="s" r="N15" s="4">
         <v>52</v>
       </c>
-      <c r="O15" s="5"/>
-      <c r="P15" s="5"/>
-      <c r="Q15" s="6"/>
-      <c r="R15" s="7"/>
-      <c r="S15" s="6"/>
-      <c r="T15" s="6"/>
-      <c r="U15" s="6"/>
-      <c r="V15" s="6"/>
-      <c r="W15" s="6"/>
-      <c r="X15" s="8"/>
-      <c r="Y15" s="6"/>
-      <c r="Z15" s="6"/>
-      <c r="AA15" s="8"/>
-      <c r="AB15" s="8"/>
-      <c r="AC15" s="8"/>
-      <c r="AD15" s="8"/>
-      <c r="AE15" s="6"/>
+      <c r="O15" s="5">
+        <v>16697.150000000001</v>
+      </c>
+      <c r="P15" s="5">
+        <v>16697.150000000001</v>
+      </c>
+      <c r="Q15" s="6">
+        <v>0.0073835112040772088</v>
+      </c>
+      <c r="R15" s="7">
+        <v>214</v>
+      </c>
+      <c r="S15" s="6">
+        <v>0.18888888888888888</v>
+      </c>
+      <c r="T15" s="6">
+        <v>0.29486006294487377</v>
+      </c>
+      <c r="U15" s="6">
+        <v>-0.039427525056671346</v>
+      </c>
+      <c r="V15" s="6">
+        <v>0.018252276586123981</v>
+      </c>
+      <c r="W15" s="6">
+        <v>0.0012960894523915756</v>
+      </c>
+      <c r="X15" s="8">
+        <v>23.386629670329672</v>
+      </c>
+      <c r="Y15" s="6">
+        <v>0.80219780219780223</v>
+      </c>
+      <c r="Z15" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA15" s="8">
+        <v>6.4535545023696681</v>
+      </c>
+      <c r="AB15" s="8">
+        <v>2.5166670329670326</v>
+      </c>
+      <c r="AC15" s="8">
+        <v>10.478260000000001</v>
+      </c>
+      <c r="AD15" s="8">
+        <v>17.480036263736263</v>
+      </c>
+      <c r="AE15" s="6">
+        <v>0.93406593406593408</v>
+      </c>
       <c r="AF15" s="9"/>
-      <c r="AG15" s="5"/>
+      <c r="AG15" s="5">
+        <v>-639.39999999999998</v>
+      </c>
       <c r="AH15" s="10">
         <v>5</v>
       </c>
@@ -3664,7 +3772,7 @@
         <v>19524</v>
       </c>
       <c r="B19" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C19" s="4">
         <v>44</v>
@@ -3700,25 +3808,61 @@
       <c t="s" r="N19" s="4">
         <v>52</v>
       </c>
-      <c r="O19" s="5"/>
-      <c r="P19" s="5"/>
-      <c r="Q19" s="6"/>
-      <c r="R19" s="7"/>
-      <c r="S19" s="6"/>
-      <c r="T19" s="6"/>
-      <c r="U19" s="6"/>
-      <c r="V19" s="6"/>
-      <c r="W19" s="6"/>
-      <c r="X19" s="8"/>
-      <c r="Y19" s="6"/>
-      <c r="Z19" s="6"/>
-      <c r="AA19" s="8"/>
-      <c r="AB19" s="8"/>
-      <c r="AC19" s="8"/>
-      <c r="AD19" s="8"/>
-      <c r="AE19" s="6"/>
+      <c r="O19" s="5">
+        <v>6060</v>
+      </c>
+      <c r="P19" s="5">
+        <v>6060</v>
+      </c>
+      <c r="Q19" s="6">
+        <v>0.71811075860543827</v>
+      </c>
+      <c r="R19" s="7">
+        <v>61</v>
+      </c>
+      <c r="S19" s="6">
+        <v>0.45238095238095233</v>
+      </c>
+      <c r="T19" s="6">
+        <v>0</v>
+      </c>
+      <c r="U19" s="6">
+        <v>-0.32800660066006598</v>
+      </c>
+      <c r="V19" s="6">
+        <v>0.036188778877887788</v>
+      </c>
+      <c r="W19" s="6">
+        <v>-0.00026336633663366339</v>
+      </c>
+      <c r="X19" s="8">
+        <v>35.234848484848484</v>
+      </c>
+      <c r="Y19" s="6">
+        <v>0.69696969696969702</v>
+      </c>
+      <c r="Z19" s="6">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="AA19" s="8">
+        <v>8.1932790322580651</v>
+      </c>
+      <c r="AB19" s="8">
+        <v>8.6072906249999992</v>
+      </c>
+      <c r="AC19" s="8">
+        <v>17.704764999999998</v>
+      </c>
+      <c r="AD19" s="8">
+        <v>24.259090909090908</v>
+      </c>
+      <c r="AE19" s="6">
+        <v>0.24242424242424243</v>
+      </c>
       <c r="AF19" s="9"/>
-      <c r="AG19" s="5"/>
+      <c r="AG19" s="5">
+        <v>-95.5</v>
+      </c>
       <c r="AH19" s="10">
         <v>2</v>
       </c>
@@ -4771,7 +4915,7 @@
         <v>19546</v>
       </c>
       <c r="B28" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C28" s="4">
         <v>44</v>
@@ -4807,25 +4951,61 @@
       <c t="s" r="N28" s="4">
         <v>52</v>
       </c>
-      <c r="O28" s="5"/>
-      <c r="P28" s="5"/>
-      <c r="Q28" s="6"/>
-      <c r="R28" s="7"/>
-      <c r="S28" s="6"/>
-      <c r="T28" s="6"/>
-      <c r="U28" s="6"/>
-      <c r="V28" s="6"/>
-      <c r="W28" s="6"/>
-      <c r="X28" s="8"/>
-      <c r="Y28" s="6"/>
-      <c r="Z28" s="6"/>
-      <c r="AA28" s="8"/>
-      <c r="AB28" s="8"/>
-      <c r="AC28" s="8"/>
-      <c r="AD28" s="8"/>
-      <c r="AE28" s="6"/>
+      <c r="O28" s="5">
+        <v>6912.1000000000004</v>
+      </c>
+      <c r="P28" s="5">
+        <v>6912.1000000000004</v>
+      </c>
+      <c r="Q28" s="6">
+        <v>0.28528342023250808</v>
+      </c>
+      <c r="R28" s="7">
+        <v>72</v>
+      </c>
+      <c r="S28" s="6">
+        <v>0.22033898305084754</v>
+      </c>
+      <c r="T28" s="6">
+        <v>0.00030343889700669836</v>
+      </c>
+      <c r="U28" s="6">
+        <v>-0.34913595000072334</v>
+      </c>
+      <c r="V28" s="6">
+        <v>0.06236910634973452</v>
+      </c>
+      <c r="W28" s="6">
+        <v>0.053960663184849753</v>
+      </c>
+      <c r="X28" s="8">
+        <v>34.825756818181816</v>
+      </c>
+      <c r="Y28" s="6">
+        <v>0.47727272727272729</v>
+      </c>
+      <c r="Z28" s="6">
+        <v>0.36363636363636365</v>
+      </c>
+      <c r="AA28" s="8">
+        <v>7.0787041666666664</v>
+      </c>
+      <c r="AB28" s="8">
+        <v>12.357197727272727</v>
+      </c>
+      <c r="AC28" s="8">
+        <v>19.455302</v>
+      </c>
+      <c r="AD28" s="8">
+        <v>26.375</v>
+      </c>
+      <c r="AE28" s="6">
+        <v>0.40909090909090912</v>
+      </c>
       <c r="AF28" s="9"/>
-      <c r="AG28" s="5"/>
+      <c r="AG28" s="5">
+        <v>-1229.8</v>
+      </c>
       <c r="AH28" s="10">
         <v>2</v>
       </c>
@@ -5388,7 +5568,7 @@
         <v>19553</v>
       </c>
       <c r="B33" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C33" s="4">
         <v>44</v>
@@ -5422,25 +5602,61 @@
       <c t="s" r="N33" s="4">
         <v>52</v>
       </c>
-      <c r="O33" s="5"/>
-      <c r="P33" s="5"/>
-      <c r="Q33" s="6"/>
-      <c r="R33" s="7"/>
-      <c r="S33" s="6"/>
-      <c r="T33" s="6"/>
-      <c r="U33" s="6"/>
-      <c r="V33" s="6"/>
-      <c r="W33" s="6"/>
-      <c r="X33" s="8"/>
-      <c r="Y33" s="6"/>
-      <c r="Z33" s="6"/>
-      <c r="AA33" s="8"/>
-      <c r="AB33" s="8"/>
-      <c r="AC33" s="8"/>
-      <c r="AD33" s="8"/>
-      <c r="AE33" s="6"/>
+      <c r="O33" s="5">
+        <v>5353.25</v>
+      </c>
+      <c r="P33" s="5">
+        <v>5353.25</v>
+      </c>
+      <c r="Q33" s="6">
+        <v>-0.0088593064375775965</v>
+      </c>
+      <c r="R33" s="7">
+        <v>42</v>
+      </c>
+      <c r="S33" s="6">
+        <v>-0.1428571428571429</v>
+      </c>
+      <c r="T33" s="6">
+        <v>0.32255082426563303</v>
+      </c>
+      <c r="U33" s="6">
+        <v>0.020554840517442677</v>
+      </c>
+      <c r="V33" s="6">
+        <v>0.021429131835800683</v>
+      </c>
+      <c r="W33" s="6">
+        <v>-0.014915145005370568</v>
+      </c>
+      <c r="X33" s="8">
+        <v>23.180458620689656</v>
+      </c>
+      <c r="Y33" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z33" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA33" s="8">
+        <v>3.9150785714285714</v>
+      </c>
+      <c r="AB33" s="8">
+        <v>4.8735620689655175</v>
+      </c>
+      <c r="AC33" s="8">
+        <v>8.8114939999999997</v>
+      </c>
+      <c r="AD33" s="8">
+        <v>15.778162068965518</v>
+      </c>
+      <c r="AE33" s="6">
+        <v>0.89655172413793105</v>
+      </c>
       <c r="AF33" s="9"/>
-      <c r="AG33" s="5"/>
+      <c r="AG33" s="5">
+        <v>0</v>
+      </c>
       <c r="AH33" s="10">
         <v>5</v>
       </c>
@@ -5666,10 +5882,10 @@
         <v>0.5714285714285714</v>
       </c>
       <c r="T35" s="6">
-        <v>-0.72243806074574035</v>
+        <v>3.7077108541169368</v>
       </c>
       <c r="U35" s="6">
-        <v>-1.0900094657996542</v>
+        <v>3.340139449063023</v>
       </c>
       <c r="V35" s="6">
         <v>0.083485094795182041</v>
@@ -6140,7 +6356,7 @@
         <v>19565</v>
       </c>
       <c r="B39" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C39" s="4">
         <v>44</v>
@@ -6176,25 +6392,61 @@
       <c t="s" r="N39" s="4">
         <v>52</v>
       </c>
-      <c r="O39" s="5"/>
-      <c r="P39" s="5"/>
-      <c r="Q39" s="6"/>
-      <c r="R39" s="7"/>
-      <c r="S39" s="6"/>
-      <c r="T39" s="6"/>
-      <c r="U39" s="6"/>
-      <c r="V39" s="6"/>
-      <c r="W39" s="6"/>
-      <c r="X39" s="8"/>
-      <c r="Y39" s="6"/>
-      <c r="Z39" s="6"/>
-      <c r="AA39" s="8"/>
-      <c r="AB39" s="8"/>
-      <c r="AC39" s="8"/>
-      <c r="AD39" s="8"/>
-      <c r="AE39" s="6"/>
+      <c r="O39" s="5">
+        <v>5129.0299999999997</v>
+      </c>
+      <c r="P39" s="5">
+        <v>5129.0299999999997</v>
+      </c>
+      <c r="Q39" s="6">
+        <v>0.57250206947297433</v>
+      </c>
+      <c r="R39" s="7">
+        <v>60</v>
+      </c>
+      <c r="S39" s="6">
+        <v>0.875</v>
+      </c>
+      <c r="T39" s="6">
+        <v>0.27647426511445633</v>
+      </c>
+      <c r="U39" s="6">
+        <v>-0.036620023669192814</v>
+      </c>
+      <c r="V39" s="6">
+        <v>0.081117287284340311</v>
+      </c>
+      <c r="W39" s="6">
+        <v>0.03709336853167168</v>
+      </c>
+      <c r="X39" s="8">
+        <v>22.050832500000002</v>
+      </c>
+      <c r="Y39" s="6">
+        <v>0.84999999999999998</v>
+      </c>
+      <c r="Z39" s="6">
+        <v>0.050000000000000003</v>
+      </c>
+      <c r="AA39" s="8">
+        <v>3.192622950819672</v>
+      </c>
+      <c r="AB39" s="8">
+        <v>6.9185194444444447</v>
+      </c>
+      <c r="AC39" s="8">
+        <v>9.7760180000000005</v>
+      </c>
+      <c r="AD39" s="8">
+        <v>16.6895825</v>
+      </c>
+      <c r="AE39" s="6">
+        <v>0.82499999999999996</v>
+      </c>
       <c r="AF39" s="9"/>
-      <c r="AG39" s="5"/>
+      <c r="AG39" s="5">
+        <v>0</v>
+      </c>
       <c r="AH39" s="10">
         <v>4</v>
       </c>
@@ -7503,7 +7755,7 @@
         <v>19601</v>
       </c>
       <c r="B50" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C50" s="4">
         <v>44</v>
@@ -7539,25 +7791,61 @@
       <c t="s" r="N50" s="4">
         <v>52</v>
       </c>
-      <c r="O50" s="5"/>
-      <c r="P50" s="5"/>
-      <c r="Q50" s="6"/>
-      <c r="R50" s="7"/>
-      <c r="S50" s="6"/>
-      <c r="T50" s="6"/>
-      <c r="U50" s="6"/>
-      <c r="V50" s="6"/>
-      <c r="W50" s="6"/>
-      <c r="X50" s="8"/>
-      <c r="Y50" s="6"/>
-      <c r="Z50" s="6"/>
-      <c r="AA50" s="8"/>
-      <c r="AB50" s="8"/>
-      <c r="AC50" s="8"/>
-      <c r="AD50" s="8"/>
-      <c r="AE50" s="6"/>
+      <c r="O50" s="5">
+        <v>3292.8099999999999</v>
+      </c>
+      <c r="P50" s="5">
+        <v>3292.8099999999999</v>
+      </c>
+      <c r="Q50" s="6">
+        <v>-0.043916191936261284</v>
+      </c>
+      <c r="R50" s="7">
+        <v>43</v>
+      </c>
+      <c r="S50" s="6">
+        <v>-0.085106382978723416</v>
+      </c>
+      <c r="T50" s="6">
+        <v>0.25693890628369087</v>
+      </c>
+      <c r="U50" s="6">
+        <v>-0.075114871492737212</v>
+      </c>
+      <c r="V50" s="6">
+        <v>0.1205878869415484</v>
+      </c>
+      <c r="W50" s="6">
+        <v>0.053766539824648255</v>
+      </c>
+      <c r="X50" s="8">
+        <v>19.7798625</v>
+      </c>
+      <c r="Y50" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z50" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA50" s="8">
+        <v>2.2814386363636365</v>
+      </c>
+      <c r="AB50" s="8">
+        <v>3.8260869565217392</v>
+      </c>
+      <c r="AC50" s="8">
+        <v>6.249333</v>
+      </c>
+      <c r="AD50" s="8">
+        <v>13.770833333333334</v>
+      </c>
+      <c r="AE50" s="6">
+        <v>0.95833333333333337</v>
+      </c>
       <c r="AF50" s="9"/>
-      <c r="AG50" s="5"/>
+      <c r="AG50" s="5">
+        <v>0</v>
+      </c>
       <c r="AH50" s="10">
         <v>4</v>
       </c>
@@ -7598,7 +7886,7 @@
         <v>19602</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C51" s="4">
         <v>44</v>
@@ -7634,25 +7922,59 @@
       <c t="s" r="N51" s="4">
         <v>52</v>
       </c>
-      <c r="O51" s="5"/>
-      <c r="P51" s="5"/>
-      <c r="Q51" s="6"/>
-      <c r="R51" s="7"/>
-      <c r="S51" s="6"/>
-      <c r="T51" s="6"/>
-      <c r="U51" s="6"/>
-      <c r="V51" s="6"/>
-      <c r="W51" s="6"/>
-      <c r="X51" s="8"/>
-      <c r="Y51" s="6"/>
-      <c r="Z51" s="6"/>
-      <c r="AA51" s="8"/>
-      <c r="AB51" s="8"/>
+      <c r="O51" s="5">
+        <v>1419.8599999999999</v>
+      </c>
+      <c r="P51" s="5">
+        <v>1419.8599999999999</v>
+      </c>
+      <c r="Q51" s="6">
+        <v>-0.088664955070603457</v>
+      </c>
+      <c r="R51" s="7">
+        <v>15</v>
+      </c>
+      <c r="S51" s="6">
+        <v>-0.0625</v>
+      </c>
+      <c r="T51" s="6">
+        <v>-0.0036341611144760757</v>
+      </c>
+      <c r="U51" s="6">
+        <v>-0.32581381262941422</v>
+      </c>
+      <c r="V51" s="6">
+        <v>0.014409871395771415</v>
+      </c>
+      <c r="W51" s="6">
+        <v>-0.075746904624399591</v>
+      </c>
+      <c r="X51" s="8">
+        <v>29.9458375</v>
+      </c>
+      <c r="Y51" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="Z51" s="6">
+        <v>0.25</v>
+      </c>
+      <c r="AA51" s="8">
+        <v>4.0055533333333333</v>
+      </c>
+      <c r="AB51" s="8">
+        <v>18.002385714285715</v>
+      </c>
       <c r="AC51" s="8"/>
-      <c r="AD51" s="8"/>
-      <c r="AE51" s="6"/>
+      <c r="AD51" s="8">
+        <v>27.443750000000001</v>
+      </c>
+      <c r="AE51" s="6">
+        <v>0.625</v>
+      </c>
       <c r="AF51" s="9"/>
-      <c r="AG51" s="5"/>
+      <c r="AG51" s="5">
+        <v>0</v>
+      </c>
       <c r="AH51" s="10">
         <v>2</v>
       </c>
@@ -8084,7 +8406,7 @@
         <v>19615</v>
       </c>
       <c r="B55" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C55" s="4">
         <v>44</v>
@@ -8120,25 +8442,61 @@
       <c t="s" r="N55" s="4">
         <v>52</v>
       </c>
-      <c r="O55" s="5"/>
-      <c r="P55" s="5"/>
-      <c r="Q55" s="6"/>
-      <c r="R55" s="7"/>
-      <c r="S55" s="6"/>
-      <c r="T55" s="6"/>
-      <c r="U55" s="6"/>
-      <c r="V55" s="6"/>
-      <c r="W55" s="6"/>
-      <c r="X55" s="8"/>
-      <c r="Y55" s="6"/>
-      <c r="Z55" s="6"/>
-      <c r="AA55" s="8"/>
-      <c r="AB55" s="8"/>
-      <c r="AC55" s="8"/>
-      <c r="AD55" s="8"/>
-      <c r="AE55" s="6"/>
+      <c r="O55" s="5">
+        <v>4202.1000000000004</v>
+      </c>
+      <c r="P55" s="5">
+        <v>4202.1000000000004</v>
+      </c>
+      <c r="Q55" s="6">
+        <v>-0.083391501614169639</v>
+      </c>
+      <c r="R55" s="7">
+        <v>50</v>
+      </c>
+      <c r="S55" s="6">
+        <v>-0.07407407407407407</v>
+      </c>
+      <c r="T55" s="6">
+        <v>0.00020703933747412005</v>
+      </c>
+      <c r="U55" s="6">
+        <v>-0.37679731562790031</v>
+      </c>
+      <c r="V55" s="6">
+        <v>0.050571142999928605</v>
+      </c>
+      <c r="W55" s="6">
+        <v>0.018258727778967657</v>
+      </c>
+      <c r="X55" s="8">
+        <v>31.746297222222225</v>
+      </c>
+      <c r="Y55" s="6">
+        <v>0.1388888888888889</v>
+      </c>
+      <c r="Z55" s="6">
+        <v>0.1388888888888889</v>
+      </c>
+      <c r="AA55" s="8">
+        <v>3.3196963636363637</v>
+      </c>
+      <c r="AB55" s="8">
+        <v>11.204762857142857</v>
+      </c>
+      <c r="AC55" s="8">
+        <v>14.524419</v>
+      </c>
+      <c r="AD55" s="8">
+        <v>21.080091666666664</v>
+      </c>
+      <c r="AE55" s="6">
+        <v>0.44444444444444442</v>
+      </c>
       <c r="AF55" s="9"/>
-      <c r="AG55" s="5"/>
+      <c r="AG55" s="5">
+        <v>0</v>
+      </c>
       <c r="AH55" s="10">
         <v>2</v>
       </c>
@@ -8489,7 +8847,9 @@
       <c r="Z58" s="6"/>
       <c r="AA58" s="8"/>
       <c r="AB58" s="8"/>
-      <c r="AC58" s="8"/>
+      <c r="AC58" s="8">
+        <v>8.3756640000000004</v>
+      </c>
       <c r="AD58" s="8"/>
       <c r="AE58" s="6"/>
       <c r="AF58" s="9"/>
@@ -8923,7 +9283,7 @@
         <v>19625</v>
       </c>
       <c r="B62" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C62" s="4">
         <v>44</v>
@@ -8959,25 +9319,61 @@
       <c t="s" r="N62" s="4">
         <v>52</v>
       </c>
-      <c r="O62" s="5"/>
-      <c r="P62" s="5"/>
-      <c r="Q62" s="6"/>
-      <c r="R62" s="7"/>
-      <c r="S62" s="6"/>
-      <c r="T62" s="6"/>
-      <c r="U62" s="6"/>
-      <c r="V62" s="6"/>
-      <c r="W62" s="6"/>
-      <c r="X62" s="8"/>
-      <c r="Y62" s="6"/>
-      <c r="Z62" s="6"/>
-      <c r="AA62" s="8"/>
-      <c r="AB62" s="8"/>
-      <c r="AC62" s="8"/>
-      <c r="AD62" s="8"/>
-      <c r="AE62" s="6"/>
+      <c r="O62" s="5">
+        <v>3755.21</v>
+      </c>
+      <c r="P62" s="5">
+        <v>3755.21</v>
+      </c>
+      <c r="Q62" s="6">
+        <v>-0.53096928426543033</v>
+      </c>
+      <c r="R62" s="7">
+        <v>31</v>
+      </c>
+      <c r="S62" s="6">
+        <v>-0.60256410256410264</v>
+      </c>
+      <c r="T62" s="6">
+        <v>0.00012515944514421295</v>
+      </c>
+      <c r="U62" s="6">
+        <v>-0.30654211082735722</v>
+      </c>
+      <c r="V62" s="6">
+        <v>0.030796014071117195</v>
+      </c>
+      <c r="W62" s="6">
+        <v>0.011199240521834998</v>
+      </c>
+      <c r="X62" s="8">
+        <v>17.415738888888889</v>
+      </c>
+      <c r="Y62" s="6">
+        <v>0.88888888888888884</v>
+      </c>
+      <c r="Z62" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA62" s="8">
+        <v>2.6387096774193548</v>
+      </c>
+      <c r="AB62" s="8">
+        <v>2.6259277777777776</v>
+      </c>
+      <c r="AC62" s="8">
+        <v>5.5868729999999998</v>
+      </c>
+      <c r="AD62" s="8">
+        <v>12.374072222222223</v>
+      </c>
+      <c r="AE62" s="6">
+        <v>1</v>
+      </c>
       <c r="AF62" s="9"/>
-      <c r="AG62" s="5"/>
+      <c r="AG62" s="5">
+        <v>0</v>
+      </c>
       <c r="AH62" s="10">
         <v>4</v>
       </c>
@@ -9149,7 +9545,7 @@
         <v>19633</v>
       </c>
       <c r="B64" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C64" s="4">
         <v>44</v>
@@ -9183,25 +9579,61 @@
       <c t="s" r="N64" s="4">
         <v>52</v>
       </c>
-      <c r="O64" s="5"/>
-      <c r="P64" s="5"/>
-      <c r="Q64" s="6"/>
-      <c r="R64" s="7"/>
-      <c r="S64" s="6"/>
-      <c r="T64" s="6"/>
-      <c r="U64" s="6"/>
-      <c r="V64" s="6"/>
-      <c r="W64" s="6"/>
-      <c r="X64" s="8"/>
-      <c r="Y64" s="6"/>
-      <c r="Z64" s="6"/>
-      <c r="AA64" s="8"/>
-      <c r="AB64" s="8"/>
-      <c r="AC64" s="8"/>
-      <c r="AD64" s="8"/>
-      <c r="AE64" s="6"/>
+      <c r="O64" s="5">
+        <v>2972.0599999999999</v>
+      </c>
+      <c r="P64" s="5">
+        <v>2972.0599999999999</v>
+      </c>
+      <c r="Q64" s="6">
+        <v>-0.24736634184882811</v>
+      </c>
+      <c r="R64" s="7">
+        <v>37</v>
+      </c>
+      <c r="S64" s="6">
+        <v>-0.11904761904761907</v>
+      </c>
+      <c r="T64" s="6">
+        <v>-0.15518455212882648</v>
+      </c>
+      <c r="U64" s="6">
+        <v>-0.47123806383451211</v>
+      </c>
+      <c r="V64" s="6">
+        <v>0.028052764749029291</v>
+      </c>
+      <c r="W64" s="6">
+        <v>-0.031024104493179817</v>
+      </c>
+      <c r="X64" s="8">
+        <v>27.987500000000001</v>
+      </c>
+      <c r="Y64" s="6">
+        <v>0.90000000000000002</v>
+      </c>
+      <c r="Z64" s="6">
+        <v>0.10000000000000001</v>
+      </c>
+      <c r="AA64" s="8">
+        <v>4.7695228571428574</v>
+      </c>
+      <c r="AB64" s="8">
+        <v>11.341176470588236</v>
+      </c>
+      <c r="AC64" s="8">
+        <v>16.462603999999999</v>
+      </c>
+      <c r="AD64" s="8">
+        <v>20.390000000000001</v>
+      </c>
+      <c r="AE64" s="6">
+        <v>0.75</v>
+      </c>
       <c r="AF64" s="9"/>
-      <c r="AG64" s="5"/>
+      <c r="AG64" s="5">
+        <v>-54</v>
+      </c>
       <c r="AH64" s="10">
         <v>1</v>
       </c>
@@ -9982,7 +10414,7 @@
         <v>19649</v>
       </c>
       <c r="B71" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C71" s="4">
         <v>44</v>
@@ -10016,25 +10448,61 @@
       <c t="s" r="N71" s="4">
         <v>52</v>
       </c>
-      <c r="O71" s="5"/>
-      <c r="P71" s="5"/>
-      <c r="Q71" s="6"/>
-      <c r="R71" s="7"/>
-      <c r="S71" s="6"/>
-      <c r="T71" s="6"/>
-      <c r="U71" s="6"/>
-      <c r="V71" s="6"/>
-      <c r="W71" s="6"/>
-      <c r="X71" s="8"/>
-      <c r="Y71" s="6"/>
-      <c r="Z71" s="6"/>
-      <c r="AA71" s="8"/>
-      <c r="AB71" s="8"/>
-      <c r="AC71" s="8"/>
-      <c r="AD71" s="8"/>
-      <c r="AE71" s="6"/>
+      <c r="O71" s="5">
+        <v>4908.8999999999996</v>
+      </c>
+      <c r="P71" s="5">
+        <v>4908.8999999999996</v>
+      </c>
+      <c r="Q71" s="6">
+        <v>-0.028344648759921709</v>
+      </c>
+      <c r="R71" s="7">
+        <v>57</v>
+      </c>
+      <c r="S71" s="6">
+        <v>-0.050000000000000044</v>
+      </c>
+      <c r="T71" s="6">
+        <v>0.31874660310863945</v>
+      </c>
+      <c r="U71" s="6">
+        <v>-0.010001181527429771</v>
+      </c>
+      <c r="V71" s="6">
+        <v>0.078041923852594272</v>
+      </c>
+      <c r="W71" s="6">
+        <v>0.028857788914013326</v>
+      </c>
+      <c r="X71" s="8">
+        <v>21.243588461538462</v>
+      </c>
+      <c r="Y71" s="6">
+        <v>0.92307692307692313</v>
+      </c>
+      <c r="Z71" s="6">
+        <v>0.038461538461538464</v>
+      </c>
+      <c r="AA71" s="8">
+        <v>2.747755769230769</v>
+      </c>
+      <c r="AB71" s="8">
+        <v>4.3057956521739129</v>
+      </c>
+      <c r="AC71" s="8">
+        <v>7.2955399999999999</v>
+      </c>
+      <c r="AD71" s="8">
+        <v>14.476923076923075</v>
+      </c>
+      <c r="AE71" s="6">
+        <v>0.96153846153846156</v>
+      </c>
       <c r="AF71" s="9"/>
-      <c r="AG71" s="5"/>
+      <c r="AG71" s="5">
+        <v>-99</v>
+      </c>
       <c r="AH71" s="10">
         <v>4</v>
       </c>
@@ -10424,7 +10892,7 @@
         <v>19657</v>
       </c>
       <c r="B75" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C75" s="4">
         <v>44</v>
@@ -10460,25 +10928,61 @@
       <c t="s" r="N75" s="4">
         <v>52</v>
       </c>
-      <c r="O75" s="5"/>
-      <c r="P75" s="5"/>
-      <c r="Q75" s="6"/>
-      <c r="R75" s="7"/>
-      <c r="S75" s="6"/>
-      <c r="T75" s="6"/>
-      <c r="U75" s="6"/>
-      <c r="V75" s="6"/>
-      <c r="W75" s="6"/>
-      <c r="X75" s="8"/>
-      <c r="Y75" s="6"/>
-      <c r="Z75" s="6"/>
-      <c r="AA75" s="8"/>
-      <c r="AB75" s="8"/>
-      <c r="AC75" s="8"/>
-      <c r="AD75" s="8"/>
-      <c r="AE75" s="6"/>
+      <c r="O75" s="5">
+        <v>4568.2200000000003</v>
+      </c>
+      <c r="P75" s="5">
+        <v>4568.2200000000003</v>
+      </c>
+      <c r="Q75" s="6">
+        <v>-0.15252356976688097</v>
+      </c>
+      <c r="R75" s="7">
+        <v>47</v>
+      </c>
+      <c r="S75" s="6">
+        <v>-0.18965517241379315</v>
+      </c>
+      <c r="T75" s="6">
+        <v>0</v>
+      </c>
+      <c r="U75" s="6">
+        <v>-0.34101028409314782</v>
+      </c>
+      <c r="V75" s="6">
+        <v>0.066234879230860147</v>
+      </c>
+      <c r="W75" s="6">
+        <v>0.041170412107998301</v>
+      </c>
+      <c r="X75" s="8">
+        <v>21.253332</v>
+      </c>
+      <c r="Y75" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z75" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA75" s="8">
+        <v>4.162057446808511</v>
+      </c>
+      <c r="AB75" s="8">
+        <v>5.3286680000000004</v>
+      </c>
+      <c r="AC75" s="8">
+        <v>10.002666</v>
+      </c>
+      <c r="AD75" s="8">
+        <v>16.944000000000003</v>
+      </c>
+      <c r="AE75" s="6">
+        <v>0.95999999999999996</v>
+      </c>
       <c r="AF75" s="9"/>
-      <c r="AG75" s="5"/>
+      <c r="AG75" s="5">
+        <v>-312.69999999999999</v>
+      </c>
       <c r="AH75" s="10">
         <v>3</v>
       </c>
@@ -10578,7 +11082,7 @@
         <v>0.024721342191645627</v>
       </c>
       <c r="W76" s="6">
-        <v>-0.0041034534545272509</v>
+        <v>-0.0059842953279315748</v>
       </c>
       <c r="X76" s="8">
         <v>32.584397872340425</v>
@@ -11519,7 +12023,7 @@
         <v>19685</v>
       </c>
       <c r="B84" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C84" s="4">
         <v>44</v>
@@ -11555,25 +12059,61 @@
       <c t="s" r="N84" s="4">
         <v>52</v>
       </c>
-      <c r="O84" s="5"/>
-      <c r="P84" s="5"/>
-      <c r="Q84" s="6"/>
-      <c r="R84" s="7"/>
-      <c r="S84" s="6"/>
-      <c r="T84" s="6"/>
-      <c r="U84" s="6"/>
-      <c r="V84" s="6"/>
-      <c r="W84" s="6"/>
-      <c r="X84" s="8"/>
-      <c r="Y84" s="6"/>
-      <c r="Z84" s="6"/>
-      <c r="AA84" s="8"/>
-      <c r="AB84" s="8"/>
-      <c r="AC84" s="8"/>
-      <c r="AD84" s="8"/>
-      <c r="AE84" s="6"/>
+      <c r="O84" s="5">
+        <v>3432.6500000000001</v>
+      </c>
+      <c r="P84" s="5">
+        <v>3432.6500000000001</v>
+      </c>
+      <c r="Q84" s="6">
+        <v>-0.22654964962483948</v>
+      </c>
+      <c r="R84" s="7">
+        <v>37</v>
+      </c>
+      <c r="S84" s="6">
+        <v>-0.19565217391304346</v>
+      </c>
+      <c r="T84" s="6">
+        <v>0</v>
+      </c>
+      <c r="U84" s="6">
+        <v>-0.36690603469622596</v>
+      </c>
+      <c r="V84" s="6">
+        <v>0.023191411882947578</v>
+      </c>
+      <c r="W84" s="6">
+        <v>-0.029319039226253767</v>
+      </c>
+      <c r="X84" s="8">
+        <v>32.694000000000003</v>
+      </c>
+      <c r="Y84" s="6">
+        <v>0.52000000000000002</v>
+      </c>
+      <c r="Z84" s="6">
+        <v>0.16</v>
+      </c>
+      <c r="AA84" s="8">
+        <v>7.1500000000000004</v>
+      </c>
+      <c r="AB84" s="8">
+        <v>7.274240909090909</v>
+      </c>
+      <c r="AC84" s="8">
+        <v>14.990907999999999</v>
+      </c>
+      <c r="AD84" s="8">
+        <v>20.631332</v>
+      </c>
+      <c r="AE84" s="6">
+        <v>0.44</v>
+      </c>
       <c r="AF84" s="9"/>
-      <c r="AG84" s="5"/>
+      <c r="AG84" s="5">
+        <v>0</v>
+      </c>
       <c r="AH84" s="10">
         <v>2</v>
       </c>
@@ -12491,7 +13031,7 @@
         <v>19700</v>
       </c>
       <c r="B92" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C92" s="4">
         <v>44</v>
@@ -12527,25 +13067,61 @@
       <c t="s" r="N92" s="4">
         <v>52</v>
       </c>
-      <c r="O92" s="5"/>
-      <c r="P92" s="5"/>
-      <c r="Q92" s="6"/>
-      <c r="R92" s="7"/>
-      <c r="S92" s="6"/>
-      <c r="T92" s="6"/>
-      <c r="U92" s="6"/>
-      <c r="V92" s="6"/>
-      <c r="W92" s="6"/>
-      <c r="X92" s="8"/>
-      <c r="Y92" s="6"/>
-      <c r="Z92" s="6"/>
-      <c r="AA92" s="8"/>
-      <c r="AB92" s="8"/>
-      <c r="AC92" s="8"/>
-      <c r="AD92" s="8"/>
-      <c r="AE92" s="6"/>
+      <c r="O92" s="5">
+        <v>3433.6999999999998</v>
+      </c>
+      <c r="P92" s="5">
+        <v>3433.6999999999998</v>
+      </c>
+      <c r="Q92" s="6">
+        <v>0.0014874876042698659</v>
+      </c>
+      <c r="R92" s="7">
+        <v>36</v>
+      </c>
+      <c r="S92" s="6">
+        <v>-0.16279069767441856</v>
+      </c>
+      <c r="T92" s="6">
+        <v>0</v>
+      </c>
+      <c r="U92" s="6">
+        <v>-0.36975565716282732</v>
+      </c>
+      <c r="V92" s="6">
+        <v>0.055363747560940098</v>
+      </c>
+      <c r="W92" s="6">
+        <v>0.043723243148789934</v>
+      </c>
+      <c r="X92" s="8">
+        <v>28.144793750000002</v>
+      </c>
+      <c r="Y92" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="Z92" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA92" s="8">
+        <v>3.4481472222222225</v>
+      </c>
+      <c r="AB92" s="8">
+        <v>2.4937499999999999</v>
+      </c>
+      <c r="AC92" s="8">
+        <v>6.328125</v>
+      </c>
+      <c r="AD92" s="8">
+        <v>14.195831249999999</v>
+      </c>
+      <c r="AE92" s="6">
+        <v>0.8125</v>
+      </c>
       <c r="AF92" s="9"/>
-      <c r="AG92" s="5"/>
+      <c r="AG92" s="5">
+        <v>0</v>
+      </c>
       <c r="AH92" s="10">
         <v>3</v>
       </c>
@@ -13277,7 +13853,9 @@
       <c r="AB98" s="8">
         <v>13.735714285714286</v>
       </c>
-      <c r="AC98" s="8"/>
+      <c r="AC98" s="8">
+        <v>26.372077000000001</v>
+      </c>
       <c r="AD98" s="8">
         <v>32.578031818181813</v>
       </c>
@@ -13459,7 +14037,7 @@
         <v>19715</v>
       </c>
       <c r="B100" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C100" s="4">
         <v>44</v>
@@ -13495,25 +14073,61 @@
       <c t="s" r="N100" s="4">
         <v>52</v>
       </c>
-      <c r="O100" s="5"/>
-      <c r="P100" s="5"/>
-      <c r="Q100" s="6"/>
-      <c r="R100" s="7"/>
-      <c r="S100" s="6"/>
-      <c r="T100" s="6"/>
-      <c r="U100" s="6"/>
-      <c r="V100" s="6"/>
-      <c r="W100" s="6"/>
-      <c r="X100" s="8"/>
-      <c r="Y100" s="6"/>
-      <c r="Z100" s="6"/>
-      <c r="AA100" s="8"/>
-      <c r="AB100" s="8"/>
-      <c r="AC100" s="8"/>
-      <c r="AD100" s="8"/>
-      <c r="AE100" s="6"/>
+      <c r="O100" s="5">
+        <v>6959.6000000000004</v>
+      </c>
+      <c r="P100" s="5">
+        <v>6959.6000000000004</v>
+      </c>
+      <c r="Q100" s="6">
+        <v>0.19660323961121917</v>
+      </c>
+      <c r="R100" s="7">
+        <v>74</v>
+      </c>
+      <c r="S100" s="6">
+        <v>0.3214285714285714</v>
+      </c>
+      <c r="T100" s="6">
+        <v>1.3962197683774931</v>
+      </c>
+      <c r="U100" s="6">
+        <v>0.98245604632450145</v>
+      </c>
+      <c r="V100" s="6">
+        <v>0.10247284326685441</v>
+      </c>
+      <c r="W100" s="6">
+        <v>0.080725903787574008</v>
+      </c>
+      <c r="X100" s="8">
+        <v>42.864645454545453</v>
+      </c>
+      <c r="Y100" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z100" s="6">
+        <v>0.27272727272727271</v>
+      </c>
+      <c r="AA100" s="8">
+        <v>14.262612162162162</v>
+      </c>
+      <c r="AB100" s="8">
+        <v>7.8968749999999996</v>
+      </c>
+      <c r="AC100" s="8">
+        <v>22.030712999999999</v>
+      </c>
+      <c r="AD100" s="8">
+        <v>31.071353125000002</v>
+      </c>
+      <c r="AE100" s="6">
+        <v>0.39393939393939392</v>
+      </c>
       <c r="AF100" s="9"/>
-      <c r="AG100" s="5"/>
+      <c r="AG100" s="5">
+        <v>-87.5</v>
+      </c>
       <c r="AH100" s="10">
         <v>3</v>
       </c>
@@ -13683,7 +14297,7 @@
         <v>19719</v>
       </c>
       <c r="B102" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C102" s="4">
         <v>44</v>
@@ -13719,25 +14333,61 @@
       <c t="s" r="N102" s="4">
         <v>52</v>
       </c>
-      <c r="O102" s="5"/>
-      <c r="P102" s="5"/>
-      <c r="Q102" s="6"/>
-      <c r="R102" s="7"/>
-      <c r="S102" s="6"/>
-      <c r="T102" s="6"/>
-      <c r="U102" s="6"/>
-      <c r="V102" s="6"/>
-      <c r="W102" s="6"/>
-      <c r="X102" s="8"/>
-      <c r="Y102" s="6"/>
-      <c r="Z102" s="6"/>
-      <c r="AA102" s="8"/>
-      <c r="AB102" s="8"/>
-      <c r="AC102" s="8"/>
-      <c r="AD102" s="8"/>
-      <c r="AE102" s="6"/>
+      <c r="O102" s="5">
+        <v>2432.9200000000001</v>
+      </c>
+      <c r="P102" s="5">
+        <v>2432.9200000000001</v>
+      </c>
+      <c r="Q102" s="6">
+        <v>-0.44897094828581974</v>
+      </c>
+      <c r="R102" s="7">
+        <v>30</v>
+      </c>
+      <c r="S102" s="6">
+        <v>-0.40000000000000002</v>
+      </c>
+      <c r="T102" s="6">
+        <v>0.00010370254673396578</v>
+      </c>
+      <c r="U102" s="6">
+        <v>-0.3688850023839666</v>
+      </c>
+      <c r="V102" s="6">
+        <v>0.019246625454186737</v>
+      </c>
+      <c r="W102" s="6">
+        <v>-0.014231664008680926</v>
+      </c>
+      <c r="X102" s="8">
+        <v>42.532499999999999</v>
+      </c>
+      <c r="Y102" s="6">
+        <v>0.20000000000000001</v>
+      </c>
+      <c r="Z102" s="6">
+        <v>0.59999999999999998</v>
+      </c>
+      <c r="AA102" s="8">
+        <v>5.0202030303030298</v>
+      </c>
+      <c r="AB102" s="8">
+        <v>15.796076470588234</v>
+      </c>
+      <c r="AC102" s="8">
+        <v>21.113502</v>
+      </c>
+      <c r="AD102" s="8">
+        <v>24.497499999999999</v>
+      </c>
+      <c r="AE102" s="6">
+        <v>0.14999999999999999</v>
+      </c>
       <c r="AF102" s="9"/>
-      <c r="AG102" s="5"/>
+      <c r="AG102" s="5">
+        <v>0</v>
+      </c>
       <c r="AH102" s="10">
         <v>2</v>
       </c>
@@ -14040,7 +14690,7 @@
         <v>19722</v>
       </c>
       <c r="B105" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C105" s="4">
         <v>44</v>
@@ -14074,25 +14724,61 @@
       <c t="s" r="N105" s="4">
         <v>52</v>
       </c>
-      <c r="O105" s="5"/>
-      <c r="P105" s="5"/>
-      <c r="Q105" s="6"/>
-      <c r="R105" s="7"/>
-      <c r="S105" s="6"/>
-      <c r="T105" s="6"/>
-      <c r="U105" s="6"/>
-      <c r="V105" s="6"/>
-      <c r="W105" s="6"/>
-      <c r="X105" s="8"/>
-      <c r="Y105" s="6"/>
-      <c r="Z105" s="6"/>
-      <c r="AA105" s="8"/>
-      <c r="AB105" s="8"/>
-      <c r="AC105" s="8"/>
-      <c r="AD105" s="8"/>
-      <c r="AE105" s="6"/>
+      <c r="O105" s="5">
+        <v>4188.6000000000004</v>
+      </c>
+      <c r="P105" s="5">
+        <v>4188.6000000000004</v>
+      </c>
+      <c r="Q105" s="6">
+        <v>-0.10395844742606786</v>
+      </c>
+      <c r="R105" s="7">
+        <v>40</v>
+      </c>
+      <c r="S105" s="6">
+        <v>-0.18367346938775508</v>
+      </c>
+      <c r="T105" s="6">
+        <v>7.1180829394069605</v>
+      </c>
+      <c r="U105" s="6">
+        <v>4.5684768657785408</v>
+      </c>
+      <c r="V105" s="6">
+        <v>0.029290932531155993</v>
+      </c>
+      <c r="W105" s="6">
+        <v>0.0030530487513727735</v>
+      </c>
+      <c r="X105" s="8">
+        <v>31.473529411764702</v>
+      </c>
+      <c r="Y105" s="6">
+        <v>0.88235294117647056</v>
+      </c>
+      <c r="Z105" s="6">
+        <v>0.17647058823529413</v>
+      </c>
+      <c r="AA105" s="8">
+        <v>5.5250000000000004</v>
+      </c>
+      <c r="AB105" s="8">
+        <v>10.502941176470589</v>
+      </c>
+      <c r="AC105" s="8">
+        <v>17.218627000000001</v>
+      </c>
+      <c r="AD105" s="8">
+        <v>23.459805882352942</v>
+      </c>
+      <c r="AE105" s="6">
+        <v>0.47058823529411764</v>
+      </c>
       <c r="AF105" s="9"/>
-      <c r="AG105" s="5"/>
+      <c r="AG105" s="5">
+        <v>0</v>
+      </c>
       <c r="AH105" s="10">
         <v>2</v>
       </c>
@@ -15373,7 +16059,9 @@
       <c r="Z116" s="6"/>
       <c r="AA116" s="8"/>
       <c r="AB116" s="8"/>
-      <c r="AC116" s="8"/>
+      <c r="AC116" s="8">
+        <v>12.646428</v>
+      </c>
       <c r="AD116" s="8"/>
       <c r="AE116" s="6"/>
       <c r="AF116" s="9"/>
@@ -15870,7 +16558,7 @@
         <v>0.023390342052313884</v>
       </c>
       <c r="W120" s="6">
-        <v>0.010213096762392538</v>
+        <v>0.011061825498445216</v>
       </c>
       <c r="X120" s="8">
         <v>26.720515384615382</v>
@@ -16458,7 +17146,7 @@
         <v>19756</v>
       </c>
       <c r="B125" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C125" s="4">
         <v>44</v>
@@ -16494,25 +17182,61 @@
       <c t="s" r="N125" s="4">
         <v>52</v>
       </c>
-      <c r="O125" s="5"/>
-      <c r="P125" s="5"/>
-      <c r="Q125" s="6"/>
-      <c r="R125" s="7"/>
-      <c r="S125" s="6"/>
-      <c r="T125" s="6"/>
-      <c r="U125" s="6"/>
-      <c r="V125" s="6"/>
-      <c r="W125" s="6"/>
-      <c r="X125" s="8"/>
-      <c r="Y125" s="6"/>
-      <c r="Z125" s="6"/>
-      <c r="AA125" s="8"/>
-      <c r="AB125" s="8"/>
-      <c r="AC125" s="8"/>
-      <c r="AD125" s="8"/>
-      <c r="AE125" s="6"/>
+      <c r="O125" s="5">
+        <v>12290.440000000001</v>
+      </c>
+      <c r="P125" s="5">
+        <v>12290.440000000001</v>
+      </c>
+      <c r="Q125" s="6">
+        <v>2.0856468579749445</v>
+      </c>
+      <c r="R125" s="7">
+        <v>69</v>
+      </c>
+      <c r="S125" s="6">
+        <v>0.46808510638297873</v>
+      </c>
+      <c r="T125" s="6">
+        <v>-0.98914286225716896</v>
+      </c>
+      <c r="U125" s="6">
+        <v>-1.3517686103996276</v>
+      </c>
+      <c r="V125" s="6">
+        <v>0.03442346246350822</v>
+      </c>
+      <c r="W125" s="6">
+        <v>0.018198656842228593</v>
+      </c>
+      <c r="X125" s="8">
+        <v>29.026999999999997</v>
+      </c>
+      <c r="Y125" s="6">
+        <v>0.76470588235294112</v>
+      </c>
+      <c r="Z125" s="6">
+        <v>0.059999999999999998</v>
+      </c>
+      <c r="AA125" s="8">
+        <v>4.6235294117647054</v>
+      </c>
+      <c r="AB125" s="8">
+        <v>8.2724489795918377</v>
+      </c>
+      <c r="AC125" s="8">
+        <v>14.971672999999999</v>
+      </c>
+      <c r="AD125" s="8">
+        <v>21.078665999999998</v>
+      </c>
+      <c r="AE125" s="6">
+        <v>0.57999999999999996</v>
+      </c>
       <c r="AF125" s="9"/>
-      <c r="AG125" s="5"/>
+      <c r="AG125" s="5">
+        <v>-130.80000000000001</v>
+      </c>
       <c r="AH125" s="10">
         <v>2</v>
       </c>
@@ -16815,7 +17539,7 @@
         <v>19762</v>
       </c>
       <c r="B128" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C128" s="4">
         <v>44</v>
@@ -16851,25 +17575,61 @@
       <c t="s" r="N128" s="4">
         <v>52</v>
       </c>
-      <c r="O128" s="5"/>
-      <c r="P128" s="5"/>
-      <c r="Q128" s="6"/>
-      <c r="R128" s="7"/>
-      <c r="S128" s="6"/>
-      <c r="T128" s="6"/>
-      <c r="U128" s="6"/>
-      <c r="V128" s="6"/>
-      <c r="W128" s="6"/>
-      <c r="X128" s="8"/>
-      <c r="Y128" s="6"/>
-      <c r="Z128" s="6"/>
-      <c r="AA128" s="8"/>
-      <c r="AB128" s="8"/>
-      <c r="AC128" s="8"/>
-      <c r="AD128" s="8"/>
-      <c r="AE128" s="6"/>
+      <c r="O128" s="5">
+        <v>1595.5</v>
+      </c>
+      <c r="P128" s="5">
+        <v>1595.5</v>
+      </c>
+      <c r="Q128" s="6">
+        <v>0.42620899258067402</v>
+      </c>
+      <c r="R128" s="7">
+        <v>24</v>
+      </c>
+      <c r="S128" s="6">
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="T128" s="6">
+        <v>-0.0082607333124412406</v>
+      </c>
+      <c r="U128" s="6">
+        <v>-0.33360701974302726</v>
+      </c>
+      <c r="V128" s="6">
+        <v>0.056423691632717016</v>
+      </c>
+      <c r="W128" s="6">
+        <v>-0.037822626136007516</v>
+      </c>
+      <c r="X128" s="8">
+        <v>37.411108333333331</v>
+      </c>
+      <c r="Y128" s="6">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="Z128" s="6">
+        <v>0.25</v>
+      </c>
+      <c r="AA128" s="8">
+        <v>5.747727272727273</v>
+      </c>
+      <c r="AB128" s="8">
+        <v>15.204166666666666</v>
+      </c>
+      <c r="AC128" s="8">
+        <v>22.043054000000001</v>
+      </c>
+      <c r="AD128" s="8">
+        <v>28.951391666666666</v>
+      </c>
+      <c r="AE128" s="6">
+        <v>0.75</v>
+      </c>
       <c r="AF128" s="9"/>
-      <c r="AG128" s="5"/>
+      <c r="AG128" s="5">
+        <v>-472.5</v>
+      </c>
       <c r="AH128" s="10">
         <v>2</v>
       </c>
@@ -19748,7 +20508,7 @@
         <v>19821</v>
       </c>
       <c r="B151" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C151" s="4">
         <v>44</v>
@@ -19784,25 +20544,61 @@
       <c t="s" r="N151" s="4">
         <v>52</v>
       </c>
-      <c r="O151" s="5"/>
-      <c r="P151" s="5"/>
-      <c r="Q151" s="6"/>
-      <c r="R151" s="7"/>
-      <c r="S151" s="6"/>
-      <c r="T151" s="6"/>
-      <c r="U151" s="6"/>
-      <c r="V151" s="6"/>
-      <c r="W151" s="6"/>
-      <c r="X151" s="8"/>
-      <c r="Y151" s="6"/>
-      <c r="Z151" s="6"/>
-      <c r="AA151" s="8"/>
-      <c r="AB151" s="8"/>
-      <c r="AC151" s="8"/>
-      <c r="AD151" s="8"/>
-      <c r="AE151" s="6"/>
+      <c r="O151" s="5">
+        <v>2151.1700000000001</v>
+      </c>
+      <c r="P151" s="5">
+        <v>2151.1700000000001</v>
+      </c>
+      <c r="Q151" s="6">
+        <v>-0.038956919544132496</v>
+      </c>
+      <c r="R151" s="7">
+        <v>29</v>
+      </c>
+      <c r="S151" s="6">
+        <v>0.26086956521739135</v>
+      </c>
+      <c r="T151" s="6">
+        <v>0.2088211531399192</v>
+      </c>
+      <c r="U151" s="6">
+        <v>-0.09873241073462348</v>
+      </c>
+      <c r="V151" s="6">
+        <v>0.078420580428325046</v>
+      </c>
+      <c r="W151" s="6">
+        <v>0.020159262168959215</v>
+      </c>
+      <c r="X151" s="8">
+        <v>21.015150000000002</v>
+      </c>
+      <c r="Y151" s="6">
+        <v>0.81818181818181823</v>
+      </c>
+      <c r="Z151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA151" s="8">
+        <v>3.564941379310345</v>
+      </c>
+      <c r="AB151" s="8">
+        <v>1.6015136363636364</v>
+      </c>
+      <c r="AC151" s="8">
+        <v>5.4143929999999996</v>
+      </c>
+      <c r="AD151" s="8">
+        <v>12.352272727272727</v>
+      </c>
+      <c r="AE151" s="6">
+        <v>0.90909090909090906</v>
+      </c>
       <c r="AF151" s="9"/>
-      <c r="AG151" s="5"/>
+      <c r="AG151" s="5">
+        <v>0</v>
+      </c>
       <c r="AH151" s="10">
         <v>5</v>
       </c>
@@ -20498,7 +21294,7 @@
         <v>19855</v>
       </c>
       <c r="B157" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C157" s="4">
         <v>44</v>
@@ -20534,25 +21330,61 @@
       <c t="s" r="N157" s="4">
         <v>52</v>
       </c>
-      <c r="O157" s="5"/>
-      <c r="P157" s="5"/>
-      <c r="Q157" s="6"/>
-      <c r="R157" s="7"/>
-      <c r="S157" s="6"/>
-      <c r="T157" s="6"/>
-      <c r="U157" s="6"/>
-      <c r="V157" s="6"/>
-      <c r="W157" s="6"/>
-      <c r="X157" s="8"/>
-      <c r="Y157" s="6"/>
-      <c r="Z157" s="6"/>
-      <c r="AA157" s="8"/>
-      <c r="AB157" s="8"/>
-      <c r="AC157" s="8"/>
-      <c r="AD157" s="8"/>
-      <c r="AE157" s="6"/>
+      <c r="O157" s="5">
+        <v>2278.48</v>
+      </c>
+      <c r="P157" s="5">
+        <v>2278.48</v>
+      </c>
+      <c r="Q157" s="6">
+        <v>-0.025132422279460109</v>
+      </c>
+      <c r="R157" s="7">
+        <v>27</v>
+      </c>
+      <c r="S157" s="6">
+        <v>-0.035714285714285698</v>
+      </c>
+      <c r="T157" s="6">
+        <v>0.30014794951019974</v>
+      </c>
+      <c r="U157" s="6">
+        <v>-0.0074035760682560304</v>
+      </c>
+      <c r="V157" s="6">
+        <v>0.059429093079596915</v>
+      </c>
+      <c r="W157" s="6">
+        <v>0.017150907622625611</v>
+      </c>
+      <c r="X157" s="8">
+        <v>24.420173684210525</v>
+      </c>
+      <c r="Y157" s="6">
+        <v>0.68421052631578949</v>
+      </c>
+      <c r="Z157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA157" s="8">
+        <v>5.2919740740740737</v>
+      </c>
+      <c r="AB157" s="8">
+        <v>3.0754368421052631</v>
+      </c>
+      <c r="AC157" s="8">
+        <v>7.8526300000000004</v>
+      </c>
+      <c r="AD157" s="8">
+        <v>14.79736842105263</v>
+      </c>
+      <c r="AE157" s="6">
+        <v>0.89473684210526316</v>
+      </c>
       <c r="AF157" s="9"/>
-      <c r="AG157" s="5"/>
+      <c r="AG157" s="5">
+        <v>0</v>
+      </c>
       <c r="AH157" s="10">
         <v>4</v>
       </c>
@@ -20593,7 +21425,7 @@
         <v>19859</v>
       </c>
       <c r="B158" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C158" s="4">
         <v>44</v>
@@ -20629,25 +21461,61 @@
       <c t="s" r="N158" s="4">
         <v>52</v>
       </c>
-      <c r="O158" s="5"/>
-      <c r="P158" s="5"/>
-      <c r="Q158" s="6"/>
-      <c r="R158" s="7"/>
-      <c r="S158" s="6"/>
-      <c r="T158" s="6"/>
-      <c r="U158" s="6"/>
-      <c r="V158" s="6"/>
-      <c r="W158" s="6"/>
-      <c r="X158" s="8"/>
-      <c r="Y158" s="6"/>
-      <c r="Z158" s="6"/>
-      <c r="AA158" s="8"/>
-      <c r="AB158" s="8"/>
-      <c r="AC158" s="8"/>
-      <c r="AD158" s="8"/>
-      <c r="AE158" s="6"/>
+      <c r="O158" s="5">
+        <v>2384.5799999999999</v>
+      </c>
+      <c r="P158" s="5">
+        <v>2384.5799999999999</v>
+      </c>
+      <c r="Q158" s="6">
+        <v>-0.23595152804567798</v>
+      </c>
+      <c r="R158" s="7">
+        <v>25</v>
+      </c>
+      <c r="S158" s="6">
+        <v>-0.2857142857142857</v>
+      </c>
+      <c r="T158" s="6">
+        <v>0.33005002977463538</v>
+      </c>
+      <c r="U158" s="6">
+        <v>0.011616594955925152</v>
+      </c>
+      <c r="V158" s="6">
+        <v>0.047273524058744104</v>
+      </c>
+      <c r="W158" s="6">
+        <v>-0.0034104538325407411</v>
+      </c>
+      <c r="X158" s="8">
+        <v>27.776665000000001</v>
+      </c>
+      <c r="Y158" s="6">
+        <v>0.90000000000000002</v>
+      </c>
+      <c r="Z158" s="6">
+        <v>0.050000000000000003</v>
+      </c>
+      <c r="AA158" s="8">
+        <v>7.1256958333333325</v>
+      </c>
+      <c r="AB158" s="8">
+        <v>3.9666684210526313</v>
+      </c>
+      <c r="AC158" s="8">
+        <v>11.621665999999999</v>
+      </c>
+      <c r="AD158" s="8">
+        <v>17.514164999999998</v>
+      </c>
+      <c r="AE158" s="6">
+        <v>0.65000000000000002</v>
+      </c>
       <c r="AF158" s="9"/>
-      <c r="AG158" s="5"/>
+      <c r="AG158" s="5">
+        <v>0</v>
+      </c>
       <c r="AH158" s="10">
         <v>2</v>
       </c>
@@ -20944,7 +21812,7 @@
         <v>19868</v>
       </c>
       <c r="B161" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C161" s="4">
         <v>44</v>
@@ -20980,25 +21848,47 @@
       <c t="s" r="N161" s="4">
         <v>52</v>
       </c>
-      <c r="O161" s="5"/>
-      <c r="P161" s="5"/>
-      <c r="Q161" s="6"/>
-      <c r="R161" s="7"/>
-      <c r="S161" s="6"/>
-      <c r="T161" s="6"/>
-      <c r="U161" s="6"/>
-      <c r="V161" s="6"/>
-      <c r="W161" s="6"/>
+      <c r="O161" s="5">
+        <v>3709.6500000000001</v>
+      </c>
+      <c r="P161" s="5">
+        <v>3709.6500000000001</v>
+      </c>
+      <c r="Q161" s="6">
+        <v>-0.027945916201556509</v>
+      </c>
+      <c r="R161" s="7">
+        <v>47</v>
+      </c>
+      <c r="S161" s="6">
+        <v>-0.060000000000000053</v>
+      </c>
+      <c r="T161" s="6">
+        <v>2.0239185637459056</v>
+      </c>
+      <c r="U161" s="6">
+        <v>1.6949630019004489</v>
+      </c>
+      <c r="V161" s="6">
+        <v>0.031287048643403016</v>
+      </c>
+      <c r="W161" s="6">
+        <v>-0.010309867507716362</v>
+      </c>
       <c r="X161" s="8"/>
       <c r="Y161" s="6"/>
       <c r="Z161" s="6"/>
-      <c r="AA161" s="8"/>
+      <c r="AA161" s="8">
+        <v>9.2595825000000005</v>
+      </c>
       <c r="AB161" s="8"/>
       <c r="AC161" s="8"/>
       <c r="AD161" s="8"/>
       <c r="AE161" s="6"/>
       <c r="AF161" s="9"/>
-      <c r="AG161" s="5"/>
+      <c r="AG161" s="5">
+        <v>-560.29999999999995</v>
+      </c>
       <c r="AH161" s="10">
         <v>5</v>
       </c>
@@ -21039,7 +21929,7 @@
         <v>19872</v>
       </c>
       <c r="B162" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C162" s="4">
         <v>44</v>
@@ -21075,25 +21965,61 @@
       <c t="s" r="N162" s="4">
         <v>52</v>
       </c>
-      <c r="O162" s="5"/>
-      <c r="P162" s="5"/>
-      <c r="Q162" s="6"/>
-      <c r="R162" s="7"/>
-      <c r="S162" s="6"/>
-      <c r="T162" s="6"/>
-      <c r="U162" s="6"/>
-      <c r="V162" s="6"/>
-      <c r="W162" s="6"/>
-      <c r="X162" s="8"/>
-      <c r="Y162" s="6"/>
-      <c r="Z162" s="6"/>
-      <c r="AA162" s="8"/>
-      <c r="AB162" s="8"/>
-      <c r="AC162" s="8"/>
-      <c r="AD162" s="8"/>
-      <c r="AE162" s="6"/>
+      <c r="O162" s="5">
+        <v>3518.5</v>
+      </c>
+      <c r="P162" s="5">
+        <v>3518.5</v>
+      </c>
+      <c r="Q162" s="6">
+        <v>-0.40014968554102459</v>
+      </c>
+      <c r="R162" s="7">
+        <v>38</v>
+      </c>
+      <c r="S162" s="6">
+        <v>-0.49333333333333329</v>
+      </c>
+      <c r="T162" s="6">
+        <v>0.29475691345743926</v>
+      </c>
+      <c r="U162" s="6">
+        <v>-0.029745004973710385</v>
+      </c>
+      <c r="V162" s="6">
+        <v>0.056986784140969166</v>
+      </c>
+      <c r="W162" s="6">
+        <v>0.035099616313770073</v>
+      </c>
+      <c r="X162" s="8">
+        <v>23.612500000000001</v>
+      </c>
+      <c r="Y162" s="6">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="Z162" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA162" s="8">
+        <v>7.0040540540540537</v>
+      </c>
+      <c r="AB162" s="8">
+        <v>4.8050739130434783</v>
+      </c>
+      <c r="AC162" s="8">
+        <v>11.836231</v>
+      </c>
+      <c r="AD162" s="8">
+        <v>18.771529166666667</v>
+      </c>
+      <c r="AE162" s="6">
+        <v>0.875</v>
+      </c>
       <c r="AF162" s="9"/>
-      <c r="AG162" s="5"/>
+      <c r="AG162" s="5">
+        <v>-270</v>
+      </c>
       <c r="AH162" s="10">
         <v>2</v>
       </c>
@@ -21396,7 +22322,7 @@
         <v>19877</v>
       </c>
       <c r="B165" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C165" s="4">
         <v>44</v>
@@ -21432,25 +22358,61 @@
       <c t="s" r="N165" s="4">
         <v>52</v>
       </c>
-      <c r="O165" s="5"/>
-      <c r="P165" s="5"/>
-      <c r="Q165" s="6"/>
-      <c r="R165" s="7"/>
-      <c r="S165" s="6"/>
-      <c r="T165" s="6"/>
-      <c r="U165" s="6"/>
-      <c r="V165" s="6"/>
-      <c r="W165" s="6"/>
-      <c r="X165" s="8"/>
-      <c r="Y165" s="6"/>
-      <c r="Z165" s="6"/>
-      <c r="AA165" s="8"/>
-      <c r="AB165" s="8"/>
-      <c r="AC165" s="8"/>
-      <c r="AD165" s="8"/>
-      <c r="AE165" s="6"/>
+      <c r="O165" s="5">
+        <v>3005.98</v>
+      </c>
+      <c r="P165" s="5">
+        <v>3005.98</v>
+      </c>
+      <c r="Q165" s="6">
+        <v>-0.34979407845783794</v>
+      </c>
+      <c r="R165" s="7">
+        <v>35</v>
+      </c>
+      <c r="S165" s="6">
+        <v>-0.40677966101694918</v>
+      </c>
+      <c r="T165" s="6">
+        <v>0.32482481586703837</v>
+      </c>
+      <c r="U165" s="6">
+        <v>0.025195410481773001</v>
+      </c>
+      <c r="V165" s="6">
+        <v>0.044025243015588925</v>
+      </c>
+      <c r="W165" s="6">
+        <v>-0.00035961649778108967</v>
+      </c>
+      <c r="X165" s="8">
+        <v>22.907894736842106</v>
+      </c>
+      <c r="Y165" s="6">
+        <v>0.89473684210526316</v>
+      </c>
+      <c r="Z165" s="6">
+        <v>0.052631578947368418</v>
+      </c>
+      <c r="AA165" s="8">
+        <v>9.0725499999999997</v>
+      </c>
+      <c r="AB165" s="8">
+        <v>1.0157894736842106</v>
+      </c>
+      <c r="AC165" s="8">
+        <v>10.435964</v>
+      </c>
+      <c r="AD165" s="8">
+        <v>17.328947368421051</v>
+      </c>
+      <c r="AE165" s="6">
+        <v>0.84210526315789469</v>
+      </c>
       <c r="AF165" s="9"/>
-      <c r="AG165" s="5"/>
+      <c r="AG165" s="5">
+        <v>24</v>
+      </c>
       <c r="AH165" s="10">
         <v>3</v>
       </c>
@@ -23446,7 +24408,7 @@
         <v>19910</v>
       </c>
       <c r="B181" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C181" s="4">
         <v>44</v>
@@ -23482,25 +24444,61 @@
       <c t="s" r="N181" s="4">
         <v>52</v>
       </c>
-      <c r="O181" s="5"/>
-      <c r="P181" s="5"/>
-      <c r="Q181" s="6"/>
-      <c r="R181" s="7"/>
-      <c r="S181" s="6"/>
-      <c r="T181" s="6"/>
-      <c r="U181" s="6"/>
-      <c r="V181" s="6"/>
-      <c r="W181" s="6"/>
-      <c r="X181" s="8"/>
-      <c r="Y181" s="6"/>
-      <c r="Z181" s="6"/>
-      <c r="AA181" s="8"/>
-      <c r="AB181" s="8"/>
-      <c r="AC181" s="8"/>
-      <c r="AD181" s="8"/>
-      <c r="AE181" s="6"/>
+      <c r="O181" s="5">
+        <v>4085.3000000000002</v>
+      </c>
+      <c r="P181" s="5">
+        <v>4085.3000000000002</v>
+      </c>
+      <c r="Q181" s="6">
+        <v>0.83137358622513724</v>
+      </c>
+      <c r="R181" s="7">
+        <v>41</v>
+      </c>
+      <c r="S181" s="6">
+        <v>0.57692307692307687</v>
+      </c>
+      <c r="T181" s="6">
+        <v>0.071664259662693061</v>
+      </c>
+      <c r="U181" s="6">
+        <v>-0.21861797175238049</v>
+      </c>
+      <c r="V181" s="6">
+        <v>0.086732920470956834</v>
+      </c>
+      <c r="W181" s="6">
+        <v>0.058421658140161058</v>
+      </c>
+      <c r="X181" s="8">
+        <v>17.478846153846153</v>
+      </c>
+      <c r="Y181" s="6">
+        <v>0.76923076923076927</v>
+      </c>
+      <c r="Z181" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA181" s="8">
+        <v>3.5654175000000001</v>
+      </c>
+      <c r="AB181" s="8">
+        <v>2.3944444444444444</v>
+      </c>
+      <c r="AC181" s="8">
+        <v>6.0822640000000003</v>
+      </c>
+      <c r="AD181" s="8">
+        <v>12.342307692307692</v>
+      </c>
+      <c r="AE181" s="6">
+        <v>1</v>
+      </c>
       <c r="AF181" s="9"/>
-      <c r="AG181" s="5"/>
+      <c r="AG181" s="5">
+        <v>0</v>
+      </c>
       <c r="AH181" s="10">
         <v>3</v>
       </c>
@@ -23672,7 +24670,7 @@
         <v>19912</v>
       </c>
       <c r="B183" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C183" s="4">
         <v>44</v>
@@ -23708,25 +24706,61 @@
       <c t="s" r="N183" s="4">
         <v>52</v>
       </c>
-      <c r="O183" s="5"/>
-      <c r="P183" s="5"/>
-      <c r="Q183" s="6"/>
-      <c r="R183" s="7"/>
-      <c r="S183" s="6"/>
-      <c r="T183" s="6"/>
-      <c r="U183" s="6"/>
-      <c r="V183" s="6"/>
-      <c r="W183" s="6"/>
-      <c r="X183" s="8"/>
-      <c r="Y183" s="6"/>
-      <c r="Z183" s="6"/>
-      <c r="AA183" s="8"/>
-      <c r="AB183" s="8"/>
-      <c r="AC183" s="8"/>
-      <c r="AD183" s="8"/>
-      <c r="AE183" s="6"/>
+      <c r="O183" s="5">
+        <v>2899.6399999999999</v>
+      </c>
+      <c r="P183" s="5">
+        <v>2899.6399999999999</v>
+      </c>
+      <c r="Q183" s="6">
+        <v>-0.14014168665838334</v>
+      </c>
+      <c r="R183" s="7">
+        <v>39</v>
+      </c>
+      <c r="S183" s="6">
+        <v>0.026315789473684292</v>
+      </c>
+      <c r="T183" s="6">
+        <v>1.8158613483053068</v>
+      </c>
+      <c r="U183" s="6">
+        <v>0.0012326357754755763</v>
+      </c>
+      <c r="V183" s="6">
+        <v>0.038073691906581511</v>
+      </c>
+      <c r="W183" s="6">
+        <v>-0.0039453173497399673</v>
+      </c>
+      <c r="X183" s="8">
+        <v>23.918516666666665</v>
+      </c>
+      <c r="Y183" s="6">
+        <v>0.55555555555555558</v>
+      </c>
+      <c r="Z183" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA183" s="8">
+        <v>5.234342424242425</v>
+      </c>
+      <c r="AB183" s="8">
+        <v>2.0127470588235297</v>
+      </c>
+      <c r="AC183" s="8">
+        <v>7.3942259999999997</v>
+      </c>
+      <c r="AD183" s="8">
+        <v>15.053705555555556</v>
+      </c>
+      <c r="AE183" s="6">
+        <v>0.83333333333333337</v>
+      </c>
       <c r="AF183" s="9"/>
-      <c r="AG183" s="5"/>
+      <c r="AG183" s="5">
+        <v>-123.8</v>
+      </c>
       <c r="AH183" s="10">
         <v>4</v>
       </c>
@@ -24086,7 +25120,7 @@
         <v>19927</v>
       </c>
       <c r="B187" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C187" s="4">
         <v>44</v>
@@ -24122,25 +25156,61 @@
       <c t="s" r="N187" s="4">
         <v>52</v>
       </c>
-      <c r="O187" s="5"/>
-      <c r="P187" s="5"/>
-      <c r="Q187" s="6"/>
-      <c r="R187" s="7"/>
-      <c r="S187" s="6"/>
-      <c r="T187" s="6"/>
-      <c r="U187" s="6"/>
-      <c r="V187" s="6"/>
-      <c r="W187" s="6"/>
-      <c r="X187" s="8"/>
-      <c r="Y187" s="6"/>
-      <c r="Z187" s="6"/>
-      <c r="AA187" s="8"/>
-      <c r="AB187" s="8"/>
-      <c r="AC187" s="8"/>
-      <c r="AD187" s="8"/>
-      <c r="AE187" s="6"/>
+      <c r="O187" s="5">
+        <v>1504.05</v>
+      </c>
+      <c r="P187" s="5">
+        <v>1504.05</v>
+      </c>
+      <c r="Q187" s="6">
+        <v>0.47009090020525846</v>
+      </c>
+      <c r="R187" s="7">
+        <v>18</v>
+      </c>
+      <c r="S187" s="6">
+        <v>0.28571428571428581</v>
+      </c>
+      <c r="T187" s="6">
+        <v>0</v>
+      </c>
+      <c r="U187" s="6">
+        <v>-0.34292742927429276</v>
+      </c>
+      <c r="V187" s="6">
+        <v>0.19953525481200757</v>
+      </c>
+      <c r="W187" s="6">
+        <v>0.13833383198696853</v>
+      </c>
+      <c r="X187" s="8">
+        <v>43.464285714285715</v>
+      </c>
+      <c r="Y187" s="6">
+        <v>0.42857142857142855</v>
+      </c>
+      <c r="Z187" s="6">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="AA187" s="8">
+        <v>8.9240722222222217</v>
+      </c>
+      <c r="AB187" s="8">
+        <v>16.323807142857142</v>
+      </c>
+      <c r="AC187" s="8">
+        <v>24.203569999999999</v>
+      </c>
+      <c r="AD187" s="8">
+        <v>31.148807142857144</v>
+      </c>
+      <c r="AE187" s="6">
+        <v>0.14285714285714285</v>
+      </c>
       <c r="AF187" s="9"/>
-      <c r="AG187" s="5"/>
+      <c r="AG187" s="5">
+        <v>-229.19999999999999</v>
+      </c>
       <c r="AH187" s="10">
         <v>1</v>
       </c>
@@ -24314,7 +25384,7 @@
         <v>19930</v>
       </c>
       <c r="B189" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C189" s="4">
         <v>44</v>
@@ -24350,25 +25420,61 @@
       <c t="s" r="N189" s="4">
         <v>52</v>
       </c>
-      <c r="O189" s="5"/>
-      <c r="P189" s="5"/>
-      <c r="Q189" s="6"/>
-      <c r="R189" s="7"/>
-      <c r="S189" s="6"/>
-      <c r="T189" s="6"/>
-      <c r="U189" s="6"/>
-      <c r="V189" s="6"/>
-      <c r="W189" s="6"/>
-      <c r="X189" s="8"/>
-      <c r="Y189" s="6"/>
-      <c r="Z189" s="6"/>
-      <c r="AA189" s="8"/>
-      <c r="AB189" s="8"/>
-      <c r="AC189" s="8"/>
-      <c r="AD189" s="8"/>
-      <c r="AE189" s="6"/>
+      <c r="O189" s="5">
+        <v>5077.6899999999996</v>
+      </c>
+      <c r="P189" s="5">
+        <v>5077.6899999999996</v>
+      </c>
+      <c r="Q189" s="6">
+        <v>0.47934098589907914</v>
+      </c>
+      <c r="R189" s="7">
+        <v>75</v>
+      </c>
+      <c r="S189" s="6">
+        <v>0.31578947368421062</v>
+      </c>
+      <c r="T189" s="6">
+        <v>0.35068682806551804</v>
+      </c>
+      <c r="U189" s="6">
+        <v>0.024428234098576324</v>
+      </c>
+      <c r="V189" s="6">
+        <v>0.040623590648503557</v>
+      </c>
+      <c r="W189" s="6">
+        <v>0.0099895818767983084</v>
+      </c>
+      <c r="X189" s="8">
+        <v>27.536923076923078</v>
+      </c>
+      <c r="Y189" s="6">
+        <v>0.15384615384615385</v>
+      </c>
+      <c r="Z189" s="6">
+        <v>0.046153846153846156</v>
+      </c>
+      <c r="AA189" s="8">
+        <v>5.1133333333333333</v>
+      </c>
+      <c r="AB189" s="8">
+        <v>11.769010937499999</v>
+      </c>
+      <c r="AC189" s="8">
+        <v>16.815726999999999</v>
+      </c>
+      <c r="AD189" s="8">
+        <v>23.562819999999999</v>
+      </c>
+      <c r="AE189" s="6">
+        <v>0.72307692307692306</v>
+      </c>
       <c r="AF189" s="9"/>
-      <c r="AG189" s="5"/>
+      <c r="AG189" s="5">
+        <v>0</v>
+      </c>
       <c r="AH189" s="10">
         <v>3</v>
       </c>
@@ -24409,7 +25515,7 @@
         <v>19931</v>
       </c>
       <c r="B190" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C190" s="4">
         <v>44</v>
@@ -24445,25 +25551,61 @@
       <c t="s" r="N190" s="4">
         <v>52</v>
       </c>
-      <c r="O190" s="5"/>
-      <c r="P190" s="5"/>
-      <c r="Q190" s="6"/>
-      <c r="R190" s="7"/>
-      <c r="S190" s="6"/>
-      <c r="T190" s="6"/>
-      <c r="U190" s="6"/>
-      <c r="V190" s="6"/>
-      <c r="W190" s="6"/>
-      <c r="X190" s="8"/>
-      <c r="Y190" s="6"/>
-      <c r="Z190" s="6"/>
-      <c r="AA190" s="8"/>
-      <c r="AB190" s="8"/>
-      <c r="AC190" s="8"/>
-      <c r="AD190" s="8"/>
-      <c r="AE190" s="6"/>
+      <c r="O190" s="5">
+        <v>3315.5500000000002</v>
+      </c>
+      <c r="P190" s="5">
+        <v>3315.5500000000002</v>
+      </c>
+      <c r="Q190" s="6">
+        <v>-0.20755127356337222</v>
+      </c>
+      <c r="R190" s="7">
+        <v>42</v>
+      </c>
+      <c r="S190" s="6">
+        <v>-0.125</v>
+      </c>
+      <c r="T190" s="6">
+        <v>-3.4667057954185583</v>
+      </c>
+      <c r="U190" s="6">
+        <v>-3.7930015834476931</v>
+      </c>
+      <c r="V190" s="6">
+        <v>0.06719292425087843</v>
+      </c>
+      <c r="W190" s="6">
+        <v>0.034763915489134531</v>
+      </c>
+      <c r="X190" s="8">
+        <v>23.568886666666668</v>
+      </c>
+      <c r="Y190" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z190" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA190" s="8">
+        <v>9.1504174999999996</v>
+      </c>
+      <c r="AB190" s="8">
+        <v>6.0583357142857137</v>
+      </c>
+      <c r="AC190" s="8">
+        <v>22.717155999999999</v>
+      </c>
+      <c r="AD190" s="8">
+        <v>15.941113333333334</v>
+      </c>
+      <c r="AE190" s="6">
+        <v>0.73333333333333328</v>
+      </c>
       <c r="AF190" s="9"/>
-      <c r="AG190" s="5"/>
+      <c r="AG190" s="5">
+        <v>-61.899999999999999</v>
+      </c>
       <c r="AH190" s="10">
         <v>2</v>
       </c>
@@ -25550,7 +26692,7 @@
         <v>19951</v>
       </c>
       <c r="B199" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C199" s="4">
         <v>44</v>
@@ -25586,25 +26728,61 @@
       <c t="s" r="N199" s="4">
         <v>52</v>
       </c>
-      <c r="O199" s="5"/>
-      <c r="P199" s="5"/>
-      <c r="Q199" s="6"/>
-      <c r="R199" s="7"/>
-      <c r="S199" s="6"/>
-      <c r="T199" s="6"/>
-      <c r="U199" s="6"/>
-      <c r="V199" s="6"/>
-      <c r="W199" s="6"/>
-      <c r="X199" s="8"/>
-      <c r="Y199" s="6"/>
-      <c r="Z199" s="6"/>
-      <c r="AA199" s="8"/>
-      <c r="AB199" s="8"/>
-      <c r="AC199" s="8"/>
-      <c r="AD199" s="8"/>
-      <c r="AE199" s="6"/>
+      <c r="O199" s="5">
+        <v>3158.3600000000001</v>
+      </c>
+      <c r="P199" s="5">
+        <v>3158.3600000000001</v>
+      </c>
+      <c r="Q199" s="6">
+        <v>-0.19488948198904377</v>
+      </c>
+      <c r="R199" s="7">
+        <v>32</v>
+      </c>
+      <c r="S199" s="6">
+        <v>-0.31914893617021278</v>
+      </c>
+      <c r="T199" s="6">
+        <v>0.34513453184564136</v>
+      </c>
+      <c r="U199" s="6">
+        <v>1.5546042883015234E-05</v>
+      </c>
+      <c r="V199" s="6">
+        <v>0.020126109753163032</v>
+      </c>
+      <c r="W199" s="6">
+        <v>-0.014654599222381236</v>
+      </c>
+      <c r="X199" s="8">
+        <v>24.032538095238095</v>
+      </c>
+      <c r="Y199" s="6">
+        <v>0.38095238095238093</v>
+      </c>
+      <c r="Z199" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA199" s="8">
+        <v>4.4849451612903222</v>
+      </c>
+      <c r="AB199" s="8">
+        <v>4.9611095238095242</v>
+      </c>
+      <c r="AC199" s="8">
+        <v>9.7626980000000003</v>
+      </c>
+      <c r="AD199" s="8">
+        <v>16.701585714285713</v>
+      </c>
+      <c r="AE199" s="6">
+        <v>0.76190476190476186</v>
+      </c>
       <c r="AF199" s="9"/>
-      <c r="AG199" s="5"/>
+      <c r="AG199" s="5">
+        <v>-50</v>
+      </c>
       <c r="AH199" s="10">
         <v>1</v>
       </c>
@@ -26145,10 +27323,10 @@
         <v>-0.52000000000000002</v>
       </c>
       <c r="T204" s="6">
-        <v>0.36896540758442337</v>
+        <v>0.35224025290764294</v>
       </c>
       <c r="U204" s="6">
-        <v>0.032628172452334299</v>
+        <v>0.015903017775553818</v>
       </c>
       <c r="V204" s="6">
         <v>0.054654800708964474</v>
@@ -26224,7 +27402,7 @@
         <v>19959</v>
       </c>
       <c r="B205" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C205" s="4">
         <v>44</v>
@@ -26260,25 +27438,57 @@
       <c t="s" r="N205" s="4">
         <v>52</v>
       </c>
-      <c r="O205" s="5"/>
-      <c r="P205" s="5"/>
+      <c r="O205" s="5">
+        <v>2515.3000000000002</v>
+      </c>
+      <c r="P205" s="5">
+        <v>2515.3000000000002</v>
+      </c>
       <c r="Q205" s="6"/>
-      <c r="R205" s="7"/>
+      <c r="R205" s="7">
+        <v>30</v>
+      </c>
       <c r="S205" s="6"/>
-      <c r="T205" s="6"/>
-      <c r="U205" s="6"/>
-      <c r="V205" s="6"/>
-      <c r="W205" s="6"/>
-      <c r="X205" s="8"/>
-      <c r="Y205" s="6"/>
-      <c r="Z205" s="6"/>
-      <c r="AA205" s="8"/>
-      <c r="AB205" s="8"/>
-      <c r="AC205" s="8"/>
-      <c r="AD205" s="8"/>
-      <c r="AE205" s="6"/>
+      <c r="T205" s="6">
+        <v>0.07386438993360632</v>
+      </c>
+      <c r="U205" s="6">
+        <v>-0.26370965689977338</v>
+      </c>
+      <c r="V205" s="6">
+        <v>0.065616825030811426</v>
+      </c>
+      <c r="W205" s="6">
+        <v>0.025494374428497595</v>
+      </c>
+      <c r="X205" s="8">
+        <v>18.408333333333335</v>
+      </c>
+      <c r="Y205" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z205" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA205" s="8">
+        <v>4.9249999999999998</v>
+      </c>
+      <c r="AB205" s="8">
+        <v>3.5111111111111111</v>
+      </c>
+      <c r="AC205" s="8">
+        <v>8.199999</v>
+      </c>
+      <c r="AD205" s="8">
+        <v>15.011111111111111</v>
+      </c>
+      <c r="AE205" s="6">
+        <v>0.75</v>
+      </c>
       <c r="AF205" s="9"/>
-      <c r="AG205" s="5"/>
+      <c r="AG205" s="5">
+        <v>-145.40000000000001</v>
+      </c>
       <c r="AH205" s="10">
         <v>3</v>
       </c>
@@ -26319,7 +27529,7 @@
         <v>19961</v>
       </c>
       <c r="B206" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C206" s="4">
         <v>44</v>
@@ -26355,25 +27565,57 @@
       <c t="s" r="N206" s="4">
         <v>52</v>
       </c>
-      <c r="O206" s="5"/>
-      <c r="P206" s="5"/>
+      <c r="O206" s="5">
+        <v>1950.6300000000001</v>
+      </c>
+      <c r="P206" s="5">
+        <v>1950.6300000000001</v>
+      </c>
       <c r="Q206" s="6"/>
-      <c r="R206" s="7"/>
+      <c r="R206" s="7">
+        <v>20</v>
+      </c>
       <c r="S206" s="6"/>
-      <c r="T206" s="6"/>
-      <c r="U206" s="6"/>
-      <c r="V206" s="6"/>
-      <c r="W206" s="6"/>
-      <c r="X206" s="8"/>
-      <c r="Y206" s="6"/>
-      <c r="Z206" s="6"/>
-      <c r="AA206" s="8"/>
-      <c r="AB206" s="8"/>
-      <c r="AC206" s="8"/>
-      <c r="AD206" s="8"/>
-      <c r="AE206" s="6"/>
+      <c r="T206" s="6">
+        <v>0.14406012416501335</v>
+      </c>
+      <c r="U206" s="6">
+        <v>-0.18079389735623874</v>
+      </c>
+      <c r="V206" s="6">
+        <v>0.097713815536518964</v>
+      </c>
+      <c r="W206" s="6">
+        <v>0.078048374115029504</v>
+      </c>
+      <c r="X206" s="8">
+        <v>29.556249999999999</v>
+      </c>
+      <c r="Y206" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="Z206" s="6">
+        <v>0.125</v>
+      </c>
+      <c r="AA206" s="8">
+        <v>7.3398166666666675</v>
+      </c>
+      <c r="AB206" s="8">
+        <v>6.75</v>
+      </c>
+      <c r="AC206" s="8">
+        <v>14.164583</v>
+      </c>
+      <c r="AD206" s="8">
+        <v>21.118749999999999</v>
+      </c>
+      <c r="AE206" s="6">
+        <v>0.625</v>
+      </c>
       <c r="AF206" s="9"/>
-      <c r="AG206" s="5"/>
+      <c r="AG206" s="5">
+        <v>-173.53</v>
+      </c>
       <c r="AH206" s="10">
         <v>2</v>
       </c>
@@ -26820,7 +28062,7 @@
         <v>19966</v>
       </c>
       <c r="B211" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C211" s="4">
         <v>44</v>
@@ -26856,25 +28098,57 @@
       <c t="s" r="N211" s="4">
         <v>52</v>
       </c>
-      <c r="O211" s="5"/>
-      <c r="P211" s="5"/>
+      <c r="O211" s="5">
+        <v>2483.21</v>
+      </c>
+      <c r="P211" s="5">
+        <v>2483.21</v>
+      </c>
       <c r="Q211" s="6"/>
-      <c r="R211" s="7"/>
+      <c r="R211" s="7">
+        <v>30</v>
+      </c>
       <c r="S211" s="6"/>
-      <c r="T211" s="6"/>
-      <c r="U211" s="6"/>
-      <c r="V211" s="6"/>
-      <c r="W211" s="6"/>
-      <c r="X211" s="8"/>
-      <c r="Y211" s="6"/>
-      <c r="Z211" s="6"/>
-      <c r="AA211" s="8"/>
-      <c r="AB211" s="8"/>
-      <c r="AC211" s="8"/>
-      <c r="AD211" s="8"/>
-      <c r="AE211" s="6"/>
+      <c r="T211" s="6">
+        <v>0.54629785640360662</v>
+      </c>
+      <c r="U211" s="6">
+        <v>0.19763221797592631</v>
+      </c>
+      <c r="V211" s="6">
+        <v>0.099538097865263103</v>
+      </c>
+      <c r="W211" s="6">
+        <v>0.016931310682543964</v>
+      </c>
+      <c r="X211" s="8">
+        <v>50.162747058823527</v>
+      </c>
+      <c r="Y211" s="6">
+        <v>0.47058823529411764</v>
+      </c>
+      <c r="Z211" s="6">
+        <v>0.47058823529411764</v>
+      </c>
+      <c r="AA211" s="8">
+        <v>5.7862068965517244</v>
+      </c>
+      <c r="AB211" s="8">
+        <v>12.422918749999999</v>
+      </c>
+      <c r="AC211" s="8">
+        <v>17.872916</v>
+      </c>
+      <c r="AD211" s="8">
+        <v>24.99791875</v>
+      </c>
+      <c r="AE211" s="6">
+        <v>0.29411764705882354</v>
+      </c>
       <c r="AF211" s="9"/>
-      <c r="AG211" s="5"/>
+      <c r="AG211" s="5">
+        <v>0</v>
+      </c>
       <c r="AH211" s="10">
         <v>2</v>
       </c>
@@ -27338,7 +28612,7 @@
         <v>0.048440377994136335</v>
       </c>
       <c r="W216" s="6">
-        <v>0.017263785615876368</v>
+        <v>0.01775455430790112</v>
       </c>
       <c r="X216" s="8">
         <v>28.227358490566036</v>
